--- a/OI/eimsa/EIMSA.xlsx
+++ b/OI/eimsa/EIMSA.xlsx
@@ -5,25 +5,24 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfaicentre-my.sharepoint.com/personal/s_jaubert_poleformation-uimmcvdl_fr/Documents/00FC/OI/EIMSA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s.jaubert\OneDrive - CFAI Centre\00FC\OI\EIMSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{C04C7E49-FE8E-43DD-BE4C-D84E663D8393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63DEC527-74CC-4A48-A1C5-E9C942C65156}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1D7336-F8FE-4B79-BF3C-4767641C8042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{8766BD0D-4453-4A2B-847D-1532E12D2501}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8766BD0D-4453-4A2B-847D-1532E12D2501}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">Feuil1!$A$2:$A$9</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Feuil1!$C$2:$C$9</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Feuil1!$B$2:$B$9</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">Feuil1!$A$2:$A$9</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Feuil1!$A$4:$A$11</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Feuil1!$B$2:$B$9</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Feuil1!$B$4:$B$11</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Feuil1!$A$2:$A$9</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Feuil1!$D$2:$D$9</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Feuil1!$D$2:$D$9</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Feuil1!$A$2:$A$9</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Feuil1!$C$2:$C$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
   <si>
     <t>M1</t>
   </si>
@@ -90,15 +89,6 @@
     <t>Critère</t>
   </si>
   <si>
-    <t>Nombre</t>
-  </si>
-  <si>
-    <t>Durée Moy</t>
-  </si>
-  <si>
-    <t>Coût</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nombre </t>
   </si>
   <si>
@@ -116,12 +106,39 @@
   <si>
     <t>RANG</t>
   </si>
+  <si>
+    <t>Nombre Pannes</t>
+  </si>
+  <si>
+    <t>Coût (durée totale)</t>
+  </si>
+  <si>
+    <t>Durée Moy d'une panne</t>
+  </si>
+  <si>
+    <t>TxQ</t>
+  </si>
+  <si>
+    <t>TxPerf</t>
+  </si>
+  <si>
+    <t>Do</t>
+  </si>
+  <si>
+    <t>TRS</t>
+  </si>
+  <si>
+    <t>TRS DIRECT</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,8 +176,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -170,6 +202,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -198,10 +236,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -218,25 +257,34 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Pourcentage" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -256,84 +304,10 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.3</cx:f>
+        <cx:f>_xlchart.v1.2</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.5</cx:f>
-      </cx:numDim>
-    </cx:data>
-  </cx:chartData>
-  <cx:chart>
-    <cx:title pos="t" align="ctr" overlay="0">
-      <cx:tx>
-        <cx:txData>
-          <cx:v>Nombre de pannes</cx:v>
-        </cx:txData>
-      </cx:tx>
-      <cx:txPr>
-        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="fr-FR" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:sysClr>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-            </a:rPr>
-            <a:t>Nombre de pannes</a:t>
-          </a:r>
-        </a:p>
-      </cx:txPr>
-    </cx:title>
-    <cx:plotArea>
-      <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{7DEED5B0-FC86-467C-AF6C-AADA99A9F930}">
-          <cx:dataLabels/>
-          <cx:dataId val="0"/>
-          <cx:layoutPr>
-            <cx:aggregation/>
-          </cx:layoutPr>
-          <cx:axisId val="1"/>
-        </cx:series>
-        <cx:series layoutId="paretoLine" ownerIdx="0" uniqueId="{BE4E68AA-81DB-47A1-9E27-852AA49464A2}">
-          <cx:axisId val="2"/>
-        </cx:series>
-      </cx:plotAreaRegion>
-      <cx:axis id="0">
-        <cx:catScaling gapWidth="0"/>
-        <cx:tickLabels/>
-      </cx:axis>
-      <cx:axis id="1">
-        <cx:valScaling/>
-        <cx:majorGridlines/>
-        <cx:tickLabels/>
-      </cx:axis>
-      <cx:axis id="2">
-        <cx:valScaling max="1" min="0"/>
-        <cx:units unit="percentage"/>
-        <cx:tickLabels/>
-      </cx:axis>
-    </cx:plotArea>
-  </cx:chart>
-</cx:chartSpace>
-</file>
-
-<file path=xl/charts/chartEx2.xml><?xml version="1.0" encoding="utf-8"?>
-<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
-  <cx:chartData>
-    <cx:data id="0">
-      <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.6</cx:f>
-      </cx:strDim>
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v1.7</cx:f>
+        <cx:f>_xlchart.v1.3</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -399,15 +373,15 @@
 </cx:chartSpace>
 </file>
 
-<file path=xl/charts/chartEx3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chartEx2.xml><?xml version="1.0" encoding="utf-8"?>
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.0</cx:f>
+        <cx:f>_xlchart.v1.4</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.1</cx:f>
+        <cx:f>_xlchart.v1.5</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -451,6 +425,90 @@
           <cx:axisId val="1"/>
         </cx:series>
         <cx:series layoutId="paretoLine" ownerIdx="0" uniqueId="{15C1C1B9-43BA-450C-9FE9-B33AE6B063DE}">
+          <cx:axisId val="2"/>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="0"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="2">
+        <cx:valScaling max="1" min="0"/>
+        <cx:units unit="percentage"/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx3.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.0</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.1</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:rich>
+          <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="fr-FR" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+              </a:rPr>
+              <a:t>Nb de pannes</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr/>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+            </a:endParaRPr>
+          </a:p>
+        </cx:rich>
+      </cx:tx>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="clusteredColumn" uniqueId="{6F282456-6EB2-4F53-97CB-C60EFD79A2EB}">
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:aggregation/>
+          </cx:layoutPr>
+          <cx:axisId val="1"/>
+        </cx:series>
+        <cx:series layoutId="paretoLine" ownerIdx="0" uniqueId="{084E26F4-F643-46EE-9F7D-204A9E5AC3BB}">
           <cx:axisId val="2"/>
         </cx:series>
       </cx:plotAreaRegion>
@@ -2121,25 +2179,25 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>50504</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>58573</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>268826</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>105369</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>359423</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>18831</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>269027</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>112578</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="2" name="Graphique 1">
+            <xdr:cNvPr id="3" name="Graphique 2">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57B2985A-6608-B7D7-9310-45AA01B46159}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF89FCC8-62E7-7F8E-E7D7-8CEF4DA42A79}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2166,8 +2224,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="50504" y="2221878"/>
-              <a:ext cx="3354766" cy="2303839"/>
+              <a:off x="4086097" y="2104892"/>
+              <a:ext cx="4580926" cy="2370281"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2199,25 +2257,25 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>376367</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>166821</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>269414</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>58414</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>393742</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>174030</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>265391</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>63796</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="3" name="Graphique 2">
+            <xdr:cNvPr id="4" name="Graphique 3">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF89FCC8-62E7-7F8E-E7D7-8CEF4DA42A79}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04BE60CD-97CC-ADDF-F3E1-F5E18A2732DC}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2244,8 +2302,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3422214" y="2149851"/>
-              <a:ext cx="3824685" cy="2350789"/>
+              <a:off x="4086685" y="58414"/>
+              <a:ext cx="4576702" cy="2004905"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2277,25 +2335,25 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>223326</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>43051</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>106311</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>298664</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>48434</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>130278</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="4" name="Graphique 3">
+            <xdr:cNvPr id="5" name="Graphique 4">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04BE60CD-97CC-ADDF-F3E1-F5E18A2732DC}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81BADA94-7063-2B57-F9C1-E15B98AC0964}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2322,8 +2380,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3269173" y="223327"/>
-              <a:ext cx="3882648" cy="1988412"/>
+              <a:off x="0" y="1737852"/>
+              <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2673,8 +2731,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17F9763F-E97B-45C6-8B40-85FBF35A4B77}">
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="3" max="3" width="11.6640625" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="2"/>
@@ -2821,155 +2884,333 @@
       <c r="E29" s="4">
         <v>3</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="F29" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
       <c r="I29" s="2"/>
-      <c r="J29" s="7"/>
+      <c r="J29" s="6"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" ht="33" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B30" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C30" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="G30" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="H30" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="I30" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="J30" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I30" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J30" s="9" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B31" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="7"/>
+        <v>4</v>
+      </c>
+      <c r="C31" s="11">
+        <v>4</v>
+      </c>
+      <c r="D31" s="11">
+        <v>7</v>
+      </c>
+      <c r="E31" s="11">
+        <v>8</v>
+      </c>
+      <c r="F31" s="3">
+        <f>C31*$C$29</f>
+        <v>8</v>
+      </c>
+      <c r="G31" s="3">
+        <f>D31*$D$29</f>
+        <v>7</v>
+      </c>
+      <c r="H31" s="3">
+        <f>E31*$E$29</f>
+        <v>24</v>
+      </c>
+      <c r="I31" s="3">
+        <f>F31+G31+H31</f>
+        <v>39</v>
+      </c>
+      <c r="J31" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="7"/>
+        <v>5</v>
+      </c>
+      <c r="C32" s="11">
+        <v>8</v>
+      </c>
+      <c r="D32" s="11">
+        <v>3</v>
+      </c>
+      <c r="E32" s="11">
+        <v>6</v>
+      </c>
+      <c r="F32" s="3">
+        <f>C32*$C$29</f>
+        <v>16</v>
+      </c>
+      <c r="G32" s="3">
+        <f>D32*$D$29</f>
+        <v>3</v>
+      </c>
+      <c r="H32" s="3">
+        <f>E32*$E$29</f>
+        <v>18</v>
+      </c>
+      <c r="I32" s="3">
+        <f>F32+G32+H32</f>
+        <v>37</v>
+      </c>
+      <c r="J32" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B33" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="7"/>
+        <v>3</v>
+      </c>
+      <c r="C33" s="11">
+        <v>5</v>
+      </c>
+      <c r="D33" s="11">
+        <v>5</v>
+      </c>
+      <c r="E33" s="11">
+        <v>7</v>
+      </c>
+      <c r="F33" s="3">
+        <f>C33*$C$29</f>
+        <v>10</v>
+      </c>
+      <c r="G33" s="3">
+        <f>D33*$D$29</f>
+        <v>5</v>
+      </c>
+      <c r="H33" s="3">
+        <f>E33*$E$29</f>
+        <v>21</v>
+      </c>
+      <c r="I33" s="3">
+        <f>F33+G33+H33</f>
+        <v>36</v>
+      </c>
+      <c r="J33" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="11">
         <v>3</v>
       </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="7"/>
+      <c r="D34" s="11">
+        <v>6</v>
+      </c>
+      <c r="E34" s="11">
+        <v>5</v>
+      </c>
+      <c r="F34" s="3">
+        <f>C34*$C$29</f>
+        <v>6</v>
+      </c>
+      <c r="G34" s="3">
+        <f>D34*$D$29</f>
+        <v>6</v>
+      </c>
+      <c r="H34" s="3">
+        <f>E34*$E$29</f>
+        <v>15</v>
+      </c>
+      <c r="I34" s="3">
+        <f>F34+G34+H34</f>
+        <v>27</v>
+      </c>
+      <c r="J34" s="3">
+        <v>4</v>
+      </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B35" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="11">
+        <v>2</v>
+      </c>
+      <c r="D35" s="11">
+        <v>8</v>
+      </c>
+      <c r="E35" s="11">
         <v>4</v>
       </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="7"/>
+      <c r="F35" s="3">
+        <f>C35*$C$29</f>
+        <v>4</v>
+      </c>
+      <c r="G35" s="3">
+        <f>D35*$D$29</f>
+        <v>8</v>
+      </c>
+      <c r="H35" s="3">
+        <f>E35*$E$29</f>
+        <v>12</v>
+      </c>
+      <c r="I35" s="3">
+        <f>F35+G35+H35</f>
+        <v>24</v>
+      </c>
+      <c r="J35" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B36" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="C36" s="11">
+        <v>6</v>
+      </c>
+      <c r="D36" s="11">
+        <v>2</v>
+      </c>
+      <c r="E36" s="11">
+        <v>3</v>
+      </c>
+      <c r="F36" s="3">
+        <f>C36*$C$29</f>
+        <v>12</v>
+      </c>
+      <c r="G36" s="3">
+        <f>D36*$D$29</f>
+        <v>2</v>
+      </c>
+      <c r="H36" s="3">
+        <f>E36*$E$29</f>
+        <v>9</v>
+      </c>
+      <c r="I36" s="3">
+        <f>F36+G36+H36</f>
+        <v>23</v>
+      </c>
+      <c r="J36" s="3">
+        <v>6</v>
+      </c>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B37" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="11">
+        <v>7</v>
+      </c>
+      <c r="D37" s="11">
+        <v>1</v>
+      </c>
+      <c r="E37" s="11">
+        <v>2</v>
+      </c>
+      <c r="F37" s="3">
+        <f>C37*$C$29</f>
+        <v>14</v>
+      </c>
+      <c r="G37" s="3">
+        <f>D37*$D$29</f>
+        <v>1</v>
+      </c>
+      <c r="H37" s="3">
+        <f>E37*$E$29</f>
         <v>6</v>
       </c>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="7"/>
+      <c r="I37" s="3">
+        <f>F37+G37+H37</f>
+        <v>21</v>
+      </c>
+      <c r="J37" s="3">
+        <v>7</v>
+      </c>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B38" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="7"/>
+      <c r="C38" s="11">
+        <v>1</v>
+      </c>
+      <c r="D38" s="11">
+        <v>4</v>
+      </c>
+      <c r="E38" s="11">
+        <v>1</v>
+      </c>
+      <c r="F38" s="3">
+        <f>C38*$C$29</f>
+        <v>2</v>
+      </c>
+      <c r="G38" s="3">
+        <f>D38*$D$29</f>
+        <v>4</v>
+      </c>
+      <c r="H38" s="3">
+        <f>E38*$E$29</f>
+        <v>3</v>
+      </c>
+      <c r="I38" s="3">
+        <f>F38+G38+H38</f>
+        <v>9</v>
+      </c>
+      <c r="J38" s="3">
+        <v>8</v>
+      </c>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="C39" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
+      <c r="C39" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B31:I38">
+    <sortCondition descending="1" ref="I31:I38"/>
+  </sortState>
   <mergeCells count="2">
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="C39:E39"/>
@@ -2978,4 +3219,58 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDBD79D9-4EFD-4806-BF67-BAB844F54339}">
+  <dimension ref="E7:I10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="7" max="8" width="11.73046875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="7" spans="5:9" x14ac:dyDescent="0.45">
+      <c r="E7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="5:9" x14ac:dyDescent="0.45">
+      <c r="E8" s="13">
+        <f>270/294</f>
+        <v>0.91836734693877553</v>
+      </c>
+      <c r="F8" s="13">
+        <f>294/312</f>
+        <v>0.94230769230769229</v>
+      </c>
+      <c r="G8" s="12">
+        <f>312/450</f>
+        <v>0.69333333333333336</v>
+      </c>
+      <c r="H8" s="15">
+        <f>PRODUCT(E8:G8)</f>
+        <v>0.60000000000000009</v>
+      </c>
+    </row>
+    <row r="10" spans="5:9" x14ac:dyDescent="0.45">
+      <c r="H10" s="15">
+        <f>4.5/7.5</f>
+        <v>0.6</v>
+      </c>
+      <c r="I10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>